--- a/evaluation/datasets/phase2_semantic_calibration_v1/review_queue.xlsx
+++ b/evaluation/datasets/phase2_semantic_calibration_v1/review_queue.xlsx
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BLOCKED_EVIDENCE_REVIEW</t>
+          <t>READY_FOR_SME</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
